--- a/gd/excel/quest.xlsx
+++ b/gd/excel/quest.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -598,7 +598,111 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>新手试炼</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>击败 5 只史莱姆</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>材料收集</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>收集 10 块铁矿石</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>装备打造</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>获得火焰长剑</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1002</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>稀世挑战</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>获得传说之剑</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1003</v>
+      </c>
+      <c r="E7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>采矿专家</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>收集 5 颗魔晶石</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4002</v>
+      </c>
+      <c r="E8" t="n">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A4:E1000">
     <cfRule type="expression" priority="1" dxfId="0">

--- a/gd/excel/quest.xlsx
+++ b/gd/excel/quest.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,19 +32,13 @@
       <sz val="12"/>
     </font>
     <font>
-      <name val="Consolas"/>
-      <i val="1"/>
-      <color rgb="001B4332"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <name val="微软雅黑"/>
       <i val="1"/>
       <color rgb="00888888"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,12 +49,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C9A227"/>
         <bgColor rgb="00C9A227"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D8F3DC"/>
-        <bgColor rgb="00D8F3DC"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,18 +82,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -507,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -517,194 +502,153 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>id</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="00FFFFFF"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">id
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="00D8F3DC"/>
+              <sz val="9"/>
+            </rPr>
+            <t>int32</t>
+          </r>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="00FFFFFF"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">title
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="00D8F3DC"/>
+              <sz val="9"/>
+            </rPr>
+            <t>string[i18n]</t>
+          </r>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="00FFFFFF"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">description
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="00D8F3DC"/>
+              <sz val="9"/>
+            </rPr>
+            <t>string[i18n]</t>
+          </r>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>reward_item_id</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="00FFFFFF"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">reward_item_id
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="00D8F3DC"/>
+              <sz val="9"/>
+            </rPr>
+            <t>int32[ref:item.id]</t>
+          </r>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>required_level</t>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b val="1"/>
+              <color rgb="00FFFFFF"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">required_level
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="00D8F3DC"/>
+              <sz val="9"/>
+            </rPr>
+            <t>int32</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>int32</t>
+          <t>任务唯一ID，禁止修改</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>string[i18n]</t>
+          <t>任务标题（多语言）</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>string[i18n]</t>
+          <t>任务描述（多语言）</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>int32[ref:item.id]</t>
+          <t>奖励道具ID，关联 item.id</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>int32</t>
+          <t>接取等级要求</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>任务唯一ID，禁止修改</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>任务标题（多语言）</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>任务描述（多语言）</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>奖励道具ID，关联 item.id</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>接取等级要求</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>新手试炼</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>击败 5 只史莱姆</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>3001</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>材料收集</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>收集 10 块铁矿石</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>4001</v>
-      </c>
-      <c r="E5" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>装备打造</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>获得火焰长剑</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1002</v>
-      </c>
-      <c r="E6" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>稀世挑战</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>获得传说之剑</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1003</v>
-      </c>
-      <c r="E7" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>采矿专家</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>收集 5 颗魔晶石</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>4002</v>
-      </c>
-      <c r="E8" t="n">
-        <v>20</v>
-      </c>
-    </row>
+    <row r="3"/>
   </sheetData>
-  <conditionalFormatting sqref="A4:E1000">
+  <conditionalFormatting sqref="A3:E1000">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>

--- a/gd/excel/quest.xlsx
+++ b/gd/excel/quest.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="quest" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Quest" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -505,117 +505,32 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
-              <b val="1"/>
-              <color rgb="00FFFFFF"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">id
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <i val="1"/>
-              <color rgb="00D8F3DC"/>
-              <sz val="9"/>
-            </rPr>
-            <t>int32</t>
-          </r>
+          <t>Id
+int32</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
-              <b val="1"/>
-              <color rgb="00FFFFFF"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">title
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <i val="1"/>
-              <color rgb="00D8F3DC"/>
-              <sz val="9"/>
-            </rPr>
-            <t>string[i18n]</t>
-          </r>
+          <t>Title
+string[i18n]</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
-              <b val="1"/>
-              <color rgb="00FFFFFF"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">description
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <i val="1"/>
-              <color rgb="00D8F3DC"/>
-              <sz val="9"/>
-            </rPr>
-            <t>string[i18n]</t>
-          </r>
+          <t>Description
+string[i18n]</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
-              <b val="1"/>
-              <color rgb="00FFFFFF"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">reward_item_id
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <i val="1"/>
-              <color rgb="00D8F3DC"/>
-              <sz val="9"/>
-            </rPr>
-            <t>int32[ref:item.id]</t>
-          </r>
+          <t>RewardItemId
+int32[ref:Item.Id]</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Segoe UI"/>
-              <b val="1"/>
-              <color rgb="00FFFFFF"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">required_level
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Consolas"/>
-              <i val="1"/>
-              <color rgb="00D8F3DC"/>
-              <sz val="9"/>
-            </rPr>
-            <t>int32</t>
-          </r>
+          <t>RequiredLevel
+int32</t>
         </is>
       </c>
     </row>
@@ -637,7 +552,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>奖励道具ID，关联 item.id</t>
+          <t>奖励道具ID，关联 Item.Id</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -646,7 +561,48 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>新手冒险</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>完成你的第一次冒险</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>屠龙勇士</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>击败邪恶的巨龙</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A3:E1000">
     <cfRule type="expression" priority="1" dxfId="0">
